--- a/dsj2/products/demo/docs/evidence/render/registry.xlsx
+++ b/dsj2/products/demo/docs/evidence/render/registry.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Реестр" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Реестр'!$A$1:$Z$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Реестр'!$A$1:$AB$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z2"/>
+  <dimension ref="A1:AB2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -456,9 +456,11 @@
     <col width="16" customWidth="1" min="21" max="21"/>
     <col width="41" customWidth="1" min="22" max="22"/>
     <col width="22" customWidth="1" min="23" max="23"/>
-    <col width="16" customWidth="1" min="24" max="24"/>
+    <col width="26" customWidth="1" min="24" max="24"/>
     <col width="16" customWidth="1" min="25" max="25"/>
-    <col width="21" customWidth="1" min="26" max="26"/>
+    <col width="16" customWidth="1" min="26" max="26"/>
+    <col width="16" customWidth="1" min="27" max="27"/>
+    <col width="21" customWidth="1" min="28" max="28"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -579,15 +581,25 @@
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
+          <t>reason</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>education</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
           <t>hours</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>validUntil</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>externalBasisNumber</t>
         </is>
@@ -695,22 +707,28 @@
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
+          <t>ТЕСТ: первичное обучение</t>
+        </is>
+      </c>
+      <c r="Y2" s="2" t="inlineStr"/>
+      <c r="Z2" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="Y2" s="2" t="inlineStr">
+      <c r="AA2" s="2" t="inlineStr">
         <is>
           <t>2027-09-22</t>
         </is>
       </c>
-      <c r="Z2" s="2" t="inlineStr">
+      <c r="AB2" s="2" t="inlineStr">
         <is>
           <t>ВНЕШНИЙ-01</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Z2"/>
+  <autoFilter ref="A1:AB2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>